--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,516 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123687376</v>
+      </c>
+      <c r="B9" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kjusebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>526870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6434196</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123687377</v>
+      </c>
+      <c r="B10" t="n">
+        <v>100645</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kjusebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>526865</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6434215</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123687354</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105485</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Kjusebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>526867</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6434198</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123687372</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92247</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kjusebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>526864</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6434213</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123687355</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105485</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kjusebo, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>526866</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6434201</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kinda</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kisa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Marika Sjödin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687376</v>
+        <v>123687355</v>
       </c>
       <c r="B9" t="n">
-        <v>100645</v>
+        <v>105502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526870</v>
+        <v>526866</v>
       </c>
       <c r="R9" t="n">
-        <v>6434196</v>
+        <v>6434201</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1564,7 +1564,7 @@
         <v>123687377</v>
       </c>
       <c r="B10" t="n">
-        <v>100645</v>
+        <v>100662</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>123687354</v>
       </c>
       <c r="B11" t="n">
-        <v>105485</v>
+        <v>105502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>123687372</v>
       </c>
       <c r="B12" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123687355</v>
+        <v>123687376</v>
       </c>
       <c r="B13" t="n">
-        <v>105485</v>
+        <v>100662</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526866</v>
+        <v>526870</v>
       </c>
       <c r="R13" t="n">
-        <v>6434201</v>
+        <v>6434196</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687355</v>
+        <v>123687377</v>
       </c>
       <c r="B9" t="n">
-        <v>105502</v>
+        <v>100680</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526866</v>
+        <v>526865</v>
       </c>
       <c r="R9" t="n">
-        <v>6434201</v>
+        <v>6434215</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687377</v>
+        <v>123687355</v>
       </c>
       <c r="B10" t="n">
-        <v>100662</v>
+        <v>105518</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526865</v>
+        <v>526866</v>
       </c>
       <c r="R10" t="n">
-        <v>6434215</v>
+        <v>6434201</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687354</v>
+        <v>123687376</v>
       </c>
       <c r="B11" t="n">
-        <v>105502</v>
+        <v>100680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526867</v>
+        <v>526870</v>
       </c>
       <c r="R11" t="n">
-        <v>6434198</v>
+        <v>6434196</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123687372</v>
+        <v>123687354</v>
       </c>
       <c r="B12" t="n">
-        <v>92264</v>
+        <v>105518</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526864</v>
+        <v>526867</v>
       </c>
       <c r="R12" t="n">
-        <v>6434213</v>
+        <v>6434198</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123687376</v>
+        <v>123687372</v>
       </c>
       <c r="B13" t="n">
-        <v>100662</v>
+        <v>92269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526870</v>
+        <v>526864</v>
       </c>
       <c r="R13" t="n">
-        <v>6434196</v>
+        <v>6434213</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>123687377</v>
       </c>
       <c r="B9" t="n">
-        <v>100680</v>
+        <v>100682</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687355</v>
+        <v>123687376</v>
       </c>
       <c r="B10" t="n">
-        <v>105518</v>
+        <v>100682</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526866</v>
+        <v>526870</v>
       </c>
       <c r="R10" t="n">
-        <v>6434201</v>
+        <v>6434196</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687376</v>
+        <v>123687355</v>
       </c>
       <c r="B11" t="n">
-        <v>100680</v>
+        <v>105520</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526870</v>
+        <v>526866</v>
       </c>
       <c r="R11" t="n">
-        <v>6434196</v>
+        <v>6434201</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1768,7 +1768,7 @@
         <v>123687354</v>
       </c>
       <c r="B12" t="n">
-        <v>105518</v>
+        <v>105520</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,7 +1870,7 @@
         <v>123687372</v>
       </c>
       <c r="B13" t="n">
-        <v>92269</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687377</v>
+        <v>123687376</v>
       </c>
       <c r="B9" t="n">
-        <v>100682</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526865</v>
+        <v>526870</v>
       </c>
       <c r="R9" t="n">
-        <v>6434215</v>
+        <v>6434196</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687376</v>
+        <v>123687372</v>
       </c>
       <c r="B10" t="n">
-        <v>100682</v>
+        <v>92271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526870</v>
+        <v>526864</v>
       </c>
       <c r="R10" t="n">
-        <v>6434196</v>
+        <v>6434213</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1666,7 +1666,7 @@
         <v>123687355</v>
       </c>
       <c r="B11" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>123687354</v>
       </c>
       <c r="B12" t="n">
-        <v>105520</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123687372</v>
+        <v>123687377</v>
       </c>
       <c r="B13" t="n">
-        <v>92271</v>
+        <v>100257</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526864</v>
+        <v>526865</v>
       </c>
       <c r="R13" t="n">
-        <v>6434213</v>
+        <v>6434215</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687376</v>
+        <v>123687372</v>
       </c>
       <c r="B9" t="n">
-        <v>100257</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526870</v>
+        <v>526864</v>
       </c>
       <c r="R9" t="n">
-        <v>6434196</v>
+        <v>6434213</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687372</v>
+        <v>123687354</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526864</v>
+        <v>526867</v>
       </c>
       <c r="R10" t="n">
-        <v>6434213</v>
+        <v>6434198</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687355</v>
+        <v>123687376</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526866</v>
+        <v>526870</v>
       </c>
       <c r="R11" t="n">
-        <v>6434201</v>
+        <v>6434196</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1765,7 +1765,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123687354</v>
+        <v>123687355</v>
       </c>
       <c r="B12" t="n">
         <v>105095</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526867</v>
+        <v>526866</v>
       </c>
       <c r="R12" t="n">
-        <v>6434198</v>
+        <v>6434201</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687372</v>
+        <v>123687354</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>105095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526864</v>
+        <v>526867</v>
       </c>
       <c r="R9" t="n">
-        <v>6434213</v>
+        <v>6434198</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687354</v>
+        <v>123687372</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526867</v>
+        <v>526864</v>
       </c>
       <c r="R10" t="n">
-        <v>6434198</v>
+        <v>6434213</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687376</v>
+        <v>123687355</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526870</v>
+        <v>526866</v>
       </c>
       <c r="R11" t="n">
-        <v>6434196</v>
+        <v>6434201</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123687355</v>
+        <v>123687376</v>
       </c>
       <c r="B12" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526866</v>
+        <v>526870</v>
       </c>
       <c r="R12" t="n">
-        <v>6434201</v>
+        <v>6434196</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687354</v>
+        <v>123687372</v>
       </c>
       <c r="B9" t="n">
-        <v>105095</v>
+        <v>92271</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526867</v>
+        <v>526864</v>
       </c>
       <c r="R9" t="n">
-        <v>6434198</v>
+        <v>6434213</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687372</v>
+        <v>123687354</v>
       </c>
       <c r="B10" t="n">
-        <v>92271</v>
+        <v>105095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526864</v>
+        <v>526867</v>
       </c>
       <c r="R10" t="n">
-        <v>6434213</v>
+        <v>6434198</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687355</v>
+        <v>123687376</v>
       </c>
       <c r="B11" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526866</v>
+        <v>526870</v>
       </c>
       <c r="R11" t="n">
-        <v>6434201</v>
+        <v>6434196</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1765,10 +1765,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123687376</v>
+        <v>123687355</v>
       </c>
       <c r="B12" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,21 +1781,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>526870</v>
+        <v>526866</v>
       </c>
       <c r="R12" t="n">
-        <v>6434196</v>
+        <v>6434201</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>

--- a/artfynd/A 8237-2023 artfynd.xlsx
+++ b/artfynd/A 8237-2023 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123687372</v>
+        <v>123687377</v>
       </c>
       <c r="B9" t="n">
-        <v>92271</v>
+        <v>100257</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>526864</v>
+        <v>526865</v>
       </c>
       <c r="R9" t="n">
-        <v>6434213</v>
+        <v>6434215</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1561,10 +1561,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123687354</v>
+        <v>123687376</v>
       </c>
       <c r="B10" t="n">
-        <v>105095</v>
+        <v>100257</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>526867</v>
+        <v>526870</v>
       </c>
       <c r="R10" t="n">
-        <v>6434198</v>
+        <v>6434196</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123687376</v>
+        <v>123687354</v>
       </c>
       <c r="B11" t="n">
-        <v>100257</v>
+        <v>105095</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1679,21 +1679,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1703,10 +1703,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>526870</v>
+        <v>526867</v>
       </c>
       <c r="R11" t="n">
-        <v>6434196</v>
+        <v>6434198</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1867,10 +1867,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123687377</v>
+        <v>123687372</v>
       </c>
       <c r="B13" t="n">
-        <v>100257</v>
+        <v>92271</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1907,10 +1907,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>526865</v>
+        <v>526864</v>
       </c>
       <c r="R13" t="n">
-        <v>6434215</v>
+        <v>6434213</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
